--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6629-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6629-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FC60996-590F-44EA-A169-901C16FD5F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9955286-70E1-4B14-B31A-021575F659EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{EAD769E5-F097-4F81-9190-0C0A81369BBF}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{A04CE4C6-1785-4995-92E8-FA8580915ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="6629-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1513,29 +1513,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DE7C51-0A18-4ADE-B17D-09378777AC4C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ECFA6F7-5BA7-440D-A07D-6DBA3C5B8A6D}">
   <dimension ref="A1:X23"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="23" width="6.75" customWidth="1"/>
-    <col min="24" max="24" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="23" width="5.88671875" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1605,7 +1605,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1725,7 +1725,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1833,7 +1833,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>2024</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>30</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>30</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>9.43</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2023</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>30</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>30</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>2022</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>30</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>30</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>2021</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>30</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>30</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>2020</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>8.3800000000000008</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="49">
         <v>2019</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>7.83</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="47">
         <v>2018</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="49" t="s">
         <v>44</v>
       </c>
